--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="64">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>442.6</t>
+    <t>475.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -101,25 +101,37 @@
     <t>05일</t>
   </si>
   <si>
-    <t>596.7</t>
-  </si>
-  <si>
-    <t>2212.8</t>
+    <t>639.8</t>
+  </si>
+  <si>
+    <t>2255.9</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>597.3</t>
+  </si>
+  <si>
+    <t>2853.2</t>
   </si>
   <si>
     <t>6.0</t>
   </si>
   <si>
-    <t>22.1</t>
-  </si>
-  <si>
-    <t>06일</t>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>07일</t>
   </si>
   <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>07일</t>
   </si>
   <si>
     <t>08일</t>
@@ -605,13 +617,13 @@
         <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -619,19 +631,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -639,19 +651,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -659,19 +671,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -679,19 +691,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -699,19 +711,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -719,19 +731,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -739,19 +751,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -759,19 +771,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -779,19 +791,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -799,19 +811,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -819,19 +831,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -839,19 +851,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -859,19 +871,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -879,19 +891,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -899,19 +911,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -919,19 +931,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -939,19 +951,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -959,19 +971,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -979,19 +991,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -999,19 +1011,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1019,19 +1031,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1039,19 +1051,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1059,19 +1071,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1079,19 +1091,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1099,19 +1111,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>475.5</t>
+    <t>463.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.6</t>
   </si>
   <si>
     <t>01일</t>
@@ -131,10 +131,22 @@
     <t>07일</t>
   </si>
   <si>
+    <t>389.1</t>
+  </si>
+  <si>
+    <t>3242.3</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>32.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>08일</t>
   </si>
   <si>
     <t>09일</t>
@@ -637,13 +649,13 @@
         <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -651,19 +663,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -671,19 +683,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -691,19 +703,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -711,19 +723,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -731,19 +743,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -751,19 +763,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -771,19 +783,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -791,19 +803,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -811,19 +823,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -831,19 +843,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -851,19 +863,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -871,19 +883,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -891,19 +903,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -911,19 +923,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -931,19 +943,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -951,19 +963,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -971,19 +983,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -991,19 +1003,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1011,19 +1023,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1031,19 +1043,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1051,19 +1063,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1071,19 +1083,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1091,19 +1103,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1111,19 +1123,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="60">
   <si>
     <t>No.</t>
   </si>
@@ -35,37 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>463.2</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.6</t>
-  </si>
-  <si>
     <t>01일</t>
   </si>
   <si>
-    <t>542.4</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
     <t>02일</t>
-  </si>
-  <si>
-    <t>345.6</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>8.9</t>
   </si>
   <si>
     <t>03일</t>
@@ -505,17 +481,13 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" t="s" s="25">
+      <c r="C2" s="25"/>
+      <c r="D2" t="s" s="26">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="26">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s" s="27">
-        <v>9</v>
-      </c>
+      <c r="E2" s="27"/>
       <c r="F2" t="s" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -523,59 +495,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s" s="31">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s" s="32">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s" s="34">
-        <v>12</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="36">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="37">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s" s="38">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -583,19 +539,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -603,19 +559,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -623,19 +579,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -643,19 +599,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -663,19 +619,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -683,19 +639,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -703,19 +659,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -723,19 +679,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -743,19 +699,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -763,19 +719,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -783,19 +739,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -803,19 +759,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -823,19 +779,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -843,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -863,19 +819,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -883,19 +839,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -903,19 +859,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -923,19 +879,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -943,19 +899,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -963,19 +919,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -983,19 +939,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1003,19 +959,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1023,19 +979,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1043,19 +999,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1063,19 +1019,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1083,19 +1039,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1103,19 +1059,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1123,19 +1079,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,37 @@
     <t>평균</t>
   </si>
   <si>
+    <t>463.2</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.6</t>
+  </si>
+  <si>
     <t>01일</t>
   </si>
   <si>
+    <t>542.4</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
     <t>02일</t>
+  </si>
+  <si>
+    <t>345.6</t>
+  </si>
+  <si>
+    <t>888.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>8.9</t>
   </si>
   <si>
     <t>03일</t>
@@ -481,13 +505,17 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" t="s" s="25">
+        <v>7</v>
+      </c>
       <c r="D2" t="s" s="26">
-        <v>7</v>
-      </c>
-      <c r="E2" s="27"/>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="27">
+        <v>9</v>
+      </c>
       <c r="F2" t="s" s="28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -495,43 +523,59 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>8</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s" s="31">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s" s="32">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s" s="33">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s" s="34">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>9</v>
-      </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="36">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s" s="37">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="39">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -539,19 +583,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -559,19 +603,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -579,19 +623,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -599,19 +643,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -619,19 +663,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -639,19 +683,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -659,19 +703,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -679,19 +723,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -699,19 +743,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -719,19 +763,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -739,19 +783,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -759,19 +803,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -779,19 +823,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -799,19 +843,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -819,19 +863,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -839,19 +883,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -859,19 +903,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -879,19 +923,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -899,19 +943,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -919,19 +963,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -939,19 +983,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -959,19 +1003,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -979,19 +1023,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -999,19 +1043,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1019,19 +1063,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1039,19 +1083,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1059,19 +1103,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1079,19 +1123,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="64">
   <si>
     <t>No.</t>
   </si>
@@ -35,39 +35,15 @@
     <t>평균</t>
   </si>
   <si>
-    <t>463.2</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.6</t>
-  </si>
-  <si>
     <t>01일</t>
   </si>
   <si>
-    <t>542.4</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
-    <t>345.6</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>8.9</t>
-  </si>
-  <si>
     <t>03일</t>
   </si>
   <si>
@@ -146,10 +122,22 @@
     <t>08일</t>
   </si>
   <si>
+    <t>590.9</t>
+  </si>
+  <si>
+    <t>3833.2</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>38.3</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>09일</t>
   </si>
   <si>
     <t>10일</t>
@@ -505,17 +493,13 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" t="s" s="25">
+      <c r="C2" s="25"/>
+      <c r="D2" t="s" s="26">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="26">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s" s="27">
-        <v>9</v>
-      </c>
+      <c r="E2" s="27"/>
       <c r="F2" t="s" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -523,59 +507,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s" s="31">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s" s="32">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s" s="34">
-        <v>12</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="36">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="37">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s" s="38">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -583,19 +551,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -603,19 +571,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -623,19 +591,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -643,19 +611,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -663,19 +631,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -683,19 +651,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -703,19 +671,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -723,19 +691,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -743,19 +711,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -763,19 +731,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -783,19 +751,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -803,19 +771,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -823,19 +791,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -843,19 +811,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -863,19 +831,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -883,19 +851,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -903,19 +871,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -923,19 +891,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -943,19 +911,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -963,19 +931,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -983,19 +951,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1003,19 +971,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1023,19 +991,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1043,19 +1011,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1063,19 +1031,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1083,19 +1051,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1103,19 +1071,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1123,19 +1091,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
   <si>
     <t>No.</t>
   </si>
@@ -35,15 +35,39 @@
     <t>평균</t>
   </si>
   <si>
+    <t>494.7</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.9</t>
+  </si>
+  <si>
     <t>01일</t>
   </si>
   <si>
+    <t>542.4</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>345.6</t>
+  </si>
+  <si>
+    <t>888.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
     <t>03일</t>
   </si>
   <si>
@@ -122,10 +146,10 @@
     <t>08일</t>
   </si>
   <si>
-    <t>590.9</t>
-  </si>
-  <si>
-    <t>3833.2</t>
+    <t>591.1</t>
+  </si>
+  <si>
+    <t>3833.4</t>
   </si>
   <si>
     <t>5.9</t>
@@ -137,10 +161,22 @@
     <t>09일</t>
   </si>
   <si>
+    <t>618.8</t>
+  </si>
+  <si>
+    <t>4452.2</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>10일</t>
   </si>
   <si>
     <t>11일</t>
@@ -493,13 +529,17 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" t="s" s="25">
+        <v>7</v>
+      </c>
       <c r="D2" t="s" s="26">
-        <v>7</v>
-      </c>
-      <c r="E2" s="27"/>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="27">
+        <v>9</v>
+      </c>
       <c r="F2" t="s" s="28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -507,43 +547,59 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>8</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s" s="31">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s" s="32">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s" s="33">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s" s="34">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>9</v>
-      </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="36">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s" s="37">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="39">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -551,19 +607,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -571,19 +627,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -591,19 +647,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -611,19 +667,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -631,19 +687,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -651,19 +707,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -671,19 +727,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -691,19 +747,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -711,19 +767,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -731,19 +787,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -751,19 +807,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -771,19 +827,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -791,19 +847,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -811,19 +867,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -831,19 +887,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -851,19 +907,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -871,19 +927,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -891,19 +947,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -911,19 +967,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -931,19 +987,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -951,19 +1007,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -971,19 +1027,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -991,19 +1047,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1011,19 +1067,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1031,19 +1087,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1051,19 +1107,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1071,19 +1127,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1091,19 +1147,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -35,33 +35,120 @@
     <t>평균</t>
   </si>
   <si>
+    <t>463.2</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.6</t>
+  </si>
+  <si>
     <t>01일</t>
   </si>
   <si>
+    <t>542.4</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>345.6</t>
+  </si>
+  <si>
+    <t>888.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
     <t>03일</t>
   </si>
   <si>
+    <t>100.9</t>
+  </si>
+  <si>
+    <t>988.9</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>9.9</t>
+  </si>
+  <si>
     <t>04일</t>
   </si>
   <si>
+    <t>627.2</t>
+  </si>
+  <si>
+    <t>1616.1</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>16.2</t>
+  </si>
+  <si>
     <t>05일</t>
   </si>
   <si>
+    <t>639.8</t>
+  </si>
+  <si>
+    <t>2255.9</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
     <t>06일</t>
   </si>
   <si>
+    <t>597.3</t>
+  </si>
+  <si>
+    <t>2853.2</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>28.5</t>
+  </si>
+  <si>
     <t>07일</t>
   </si>
   <si>
+    <t>389.1</t>
+  </si>
+  <si>
+    <t>3242.3</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>32.4</t>
+  </si>
+  <si>
     <t>08일</t>
   </si>
   <si>
+    <t>0.0</t>
+  </si>
+  <si>
     <t>09일</t>
   </si>
   <si>
@@ -126,9 +213,6 @@
   </si>
   <si>
     <t>30일</t>
-  </si>
-  <si>
-    <t>0.0</t>
   </si>
   <si>
     <t>31일</t>
@@ -421,13 +505,17 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" t="s" s="25">
+        <v>7</v>
+      </c>
       <c r="D2" t="s" s="26">
-        <v>7</v>
-      </c>
-      <c r="E2" s="27"/>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="27">
+        <v>9</v>
+      </c>
       <c r="F2" t="s" s="28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -435,367 +523,599 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>8</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s" s="31">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s" s="32">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s" s="33">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s" s="34">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>9</v>
-      </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="36">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s" s="37">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="39">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>10</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="34"/>
+        <v>18</v>
+      </c>
+      <c r="C5" t="s" s="31">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s" s="32">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s" s="33">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s" s="34">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" t="n" s="1">
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>11</v>
-      </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="39"/>
+        <v>23</v>
+      </c>
+      <c r="C6" t="s" s="36">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s" s="37">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s" s="38">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s" s="39">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" t="n" s="1">
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>12</v>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="34"/>
+        <v>28</v>
+      </c>
+      <c r="C7" t="s" s="31">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s" s="32">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s" s="33">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s" s="34">
+        <v>32</v>
+      </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
       <c r="A8" t="n" s="1">
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>13</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="39"/>
+        <v>33</v>
+      </c>
+      <c r="C8" t="s" s="36">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="37">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s" s="38">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s" s="39">
+        <v>37</v>
+      </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
       <c r="A9" t="n" s="1">
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>14</v>
-      </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="34"/>
+        <v>38</v>
+      </c>
+      <c r="C9" t="s" s="31">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s" s="32">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s" s="33">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s" s="34">
+        <v>42</v>
+      </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
       <c r="A10" t="n" s="1">
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>15</v>
-      </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="39"/>
+        <v>43</v>
+      </c>
+      <c r="C10" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F10" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
       <c r="A11" t="n" s="1">
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>16</v>
-      </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="34"/>
+        <v>45</v>
+      </c>
+      <c r="C11" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F11" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
       <c r="A12" t="n" s="1">
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>17</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="39"/>
+        <v>46</v>
+      </c>
+      <c r="C12" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F12" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
       <c r="A13" t="n" s="1">
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>18</v>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="34"/>
+        <v>47</v>
+      </c>
+      <c r="C13" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F13" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
       <c r="A14" t="n" s="1">
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>19</v>
-      </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="39"/>
+        <v>48</v>
+      </c>
+      <c r="C14" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F14" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
       <c r="A15" t="n" s="1">
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>20</v>
-      </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="34"/>
+        <v>49</v>
+      </c>
+      <c r="C15" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F15" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
       <c r="A16" t="n" s="1">
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>21</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="39"/>
+        <v>50</v>
+      </c>
+      <c r="C16" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E16" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
       <c r="A17" t="n" s="1">
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>22</v>
-      </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="34"/>
+        <v>51</v>
+      </c>
+      <c r="C17" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F17" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
       <c r="A18" t="n" s="1">
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>23</v>
-      </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39"/>
+        <v>52</v>
+      </c>
+      <c r="C18" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F18" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
       <c r="A19" t="n" s="1">
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>24</v>
-      </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
+        <v>53</v>
+      </c>
+      <c r="C19" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F19" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
       <c r="A20" t="n" s="1">
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>25</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
+        <v>54</v>
+      </c>
+      <c r="C20" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F20" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
       <c r="A21" t="n" s="1">
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>26</v>
-      </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
+        <v>55</v>
+      </c>
+      <c r="C21" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F21" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
       <c r="A22" t="n" s="1">
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>27</v>
-      </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39"/>
+        <v>56</v>
+      </c>
+      <c r="C22" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F22" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
       <c r="A23" t="n" s="1">
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>28</v>
-      </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="34"/>
+        <v>57</v>
+      </c>
+      <c r="C23" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F23" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
       <c r="A24" t="n" s="1">
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>29</v>
-      </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
+        <v>58</v>
+      </c>
+      <c r="C24" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F24" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
       <c r="A25" t="n" s="1">
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>30</v>
-      </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="34"/>
+        <v>59</v>
+      </c>
+      <c r="C25" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D25" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F25" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
       <c r="A26" t="n" s="1">
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>31</v>
-      </c>
-      <c r="C26" s="36"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
+        <v>60</v>
+      </c>
+      <c r="C26" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F26" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
       <c r="A27" t="n" s="1">
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>32</v>
-      </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="34"/>
+        <v>61</v>
+      </c>
+      <c r="C27" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D27" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F27" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
       <c r="A28" t="n" s="1">
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>33</v>
-      </c>
-      <c r="C28" s="36"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
+        <v>62</v>
+      </c>
+      <c r="C28" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E28" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F28" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
       <c r="A29" t="n" s="1">
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>34</v>
-      </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="34"/>
+        <v>63</v>
+      </c>
+      <c r="C29" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D29" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F29" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
       <c r="A30" t="n" s="1">
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>35</v>
-      </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="39"/>
+        <v>64</v>
+      </c>
+      <c r="C30" t="s" s="36">
+        <v>44</v>
+      </c>
+      <c r="D30" t="s" s="37">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s" s="38">
+        <v>44</v>
+      </c>
+      <c r="F30" t="s" s="39">
+        <v>44</v>
+      </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
       <c r="A31" t="n" s="1">
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>36</v>
-      </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="34"/>
+        <v>65</v>
+      </c>
+      <c r="C31" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s" s="32">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="F31" t="s" s="34">
+        <v>44</v>
+      </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
       <c r="A32" t="n" s="1">
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -803,19 +1123,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>463.2</t>
+    <t>481.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.6</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -146,19 +146,64 @@
     <t>08일</t>
   </si>
   <si>
+    <t>591.1</t>
+  </si>
+  <si>
+    <t>3833.4</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>38.3</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>619.3</t>
+  </si>
+  <si>
+    <t>4452.7</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>585.4</t>
+  </si>
+  <si>
+    <t>5038.1</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>256.0</t>
+  </si>
+  <si>
+    <t>5294.1</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>52.9</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>12일</t>
   </si>
   <si>
     <t>13일</t>
@@ -669,13 +714,13 @@
         <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -683,19 +728,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -703,19 +748,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s" s="36">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s" s="37">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s" s="38">
         <v>46</v>
       </c>
-      <c r="C12" t="s" s="36">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s" s="37">
-        <v>44</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>44</v>
-      </c>
       <c r="F12" t="s" s="39">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -723,19 +768,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -743,19 +788,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -763,19 +808,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -783,19 +828,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -803,19 +848,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -823,19 +868,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -843,19 +888,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -863,19 +908,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -883,19 +928,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -903,19 +948,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -923,19 +968,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -943,19 +988,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -963,19 +1008,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -983,19 +1028,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1003,19 +1048,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1023,19 +1068,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1043,19 +1088,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1063,19 +1108,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1083,19 +1128,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1103,19 +1148,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1123,19 +1168,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="75">
   <si>
     <t>No.</t>
   </si>
@@ -35,37 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>481.3</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
-  </si>
-  <si>
     <t>01일</t>
   </si>
   <si>
-    <t>542.4</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
     <t>02일</t>
-  </si>
-  <si>
-    <t>345.6</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>8.9</t>
   </si>
   <si>
     <t>03일</t>
@@ -550,17 +526,13 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" t="s" s="25">
+      <c r="C2" s="25"/>
+      <c r="D2" t="s" s="26">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="26">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s" s="27">
-        <v>9</v>
-      </c>
+      <c r="E2" s="27"/>
       <c r="F2" t="s" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -568,59 +540,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s" s="31">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s" s="32">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s" s="34">
-        <v>12</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="36">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="37">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s" s="38">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -628,19 +584,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -648,19 +604,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -668,19 +624,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -688,19 +644,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -708,19 +664,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -728,19 +684,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -748,19 +704,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -768,19 +724,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -788,19 +744,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -808,19 +764,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -828,19 +784,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -848,19 +804,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -868,19 +824,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -888,19 +844,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -908,19 +864,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -928,19 +884,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -948,19 +904,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -968,19 +924,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -988,19 +944,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1008,19 +964,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1028,19 +984,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1048,19 +1004,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1068,19 +1024,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1088,19 +1044,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1108,19 +1064,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1128,19 +1084,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1148,19 +1104,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1168,19 +1124,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="86">
   <si>
     <t>No.</t>
   </si>
@@ -35,15 +35,39 @@
     <t>평균</t>
   </si>
   <si>
+    <t>481.6</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.8</t>
+  </si>
+  <si>
     <t>01일</t>
   </si>
   <si>
+    <t>542.4</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>345.6</t>
+  </si>
+  <si>
+    <t>888.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
     <t>03일</t>
   </si>
   <si>
@@ -179,10 +203,19 @@
     <t>12일</t>
   </si>
   <si>
+    <t>485.0</t>
+  </si>
+  <si>
+    <t>5779.1</t>
+  </si>
+  <si>
+    <t>57.8</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>13일</t>
   </si>
   <si>
     <t>14일</t>
@@ -526,13 +559,17 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" t="s" s="25">
+        <v>7</v>
+      </c>
       <c r="D2" t="s" s="26">
-        <v>7</v>
-      </c>
-      <c r="E2" s="27"/>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="27">
+        <v>9</v>
+      </c>
       <c r="F2" t="s" s="28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -540,43 +577,59 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>8</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s" s="31">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s" s="32">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s" s="33">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s" s="34">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>9</v>
-      </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="36">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s" s="37">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="39">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -584,19 +637,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -604,19 +657,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -624,19 +677,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -644,19 +697,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -664,19 +717,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -684,19 +737,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -704,19 +757,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s" s="37">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s" s="38">
         <v>46</v>
       </c>
-      <c r="D12" t="s" s="37">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>38</v>
-      </c>
       <c r="F12" t="s" s="39">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -724,19 +777,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -744,19 +797,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -764,19 +817,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -784,19 +837,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -804,19 +857,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -824,19 +877,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -844,19 +897,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -864,19 +917,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -884,19 +937,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -904,19 +957,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -924,19 +977,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -944,19 +997,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -964,19 +1017,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -984,19 +1037,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1004,19 +1057,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1024,19 +1077,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1044,19 +1097,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1064,19 +1117,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1084,19 +1137,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1104,19 +1157,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1124,19 +1177,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="90">
   <si>
     <t>No.</t>
   </si>
@@ -35,190 +35,202 @@
     <t>평균</t>
   </si>
   <si>
-    <t>481.6</t>
+    <t>489.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>542.4</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>345.6</t>
+  </si>
+  <si>
+    <t>888.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>100.9</t>
+  </si>
+  <si>
+    <t>988.9</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>9.9</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>627.2</t>
+  </si>
+  <si>
+    <t>1616.1</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>16.2</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>639.8</t>
+  </si>
+  <si>
+    <t>2255.9</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>597.3</t>
+  </si>
+  <si>
+    <t>2853.2</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>389.1</t>
+  </si>
+  <si>
+    <t>3242.3</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>32.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>591.1</t>
+  </si>
+  <si>
+    <t>3833.4</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>38.3</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>619.3</t>
+  </si>
+  <si>
+    <t>4452.7</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>585.4</t>
+  </si>
+  <si>
+    <t>5038.1</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>256.0</t>
+  </si>
+  <si>
+    <t>5294.1</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>52.9</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>485.0</t>
+  </si>
+  <si>
+    <t>5779.1</t>
+  </si>
+  <si>
     <t>4.8</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>542.4</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>345.6</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>8.9</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>100.9</t>
-  </si>
-  <si>
-    <t>988.9</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>9.9</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>627.2</t>
-  </si>
-  <si>
-    <t>1616.1</t>
-  </si>
-  <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>16.2</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>639.8</t>
-  </si>
-  <si>
-    <t>2255.9</t>
-  </si>
-  <si>
-    <t>6.4</t>
-  </si>
-  <si>
-    <t>22.6</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>597.3</t>
-  </si>
-  <si>
-    <t>2853.2</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>28.5</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>389.1</t>
-  </si>
-  <si>
-    <t>3242.3</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>32.4</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>591.1</t>
-  </si>
-  <si>
-    <t>3833.4</t>
-  </si>
-  <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>38.3</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>619.3</t>
-  </si>
-  <si>
-    <t>4452.7</t>
-  </si>
-  <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>44.5</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>585.4</t>
-  </si>
-  <si>
-    <t>5038.1</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>256.0</t>
-  </si>
-  <si>
-    <t>5294.1</t>
-  </si>
-  <si>
-    <t>2.6</t>
-  </si>
-  <si>
-    <t>52.9</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>485.0</t>
-  </si>
-  <si>
-    <t>5779.1</t>
-  </si>
-  <si>
     <t>57.8</t>
   </si>
   <si>
     <t>13일</t>
   </si>
   <si>
+    <t>589.9</t>
+  </si>
+  <si>
+    <t>6369.0</t>
+  </si>
+  <si>
+    <t>63.7</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>14일</t>
   </si>
   <si>
     <t>15일</t>
@@ -806,10 +818,10 @@
         <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -817,19 +829,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -837,19 +849,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -857,19 +869,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -877,19 +889,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -897,19 +909,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -917,19 +929,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -937,19 +949,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -957,19 +969,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -977,19 +989,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -997,19 +1009,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1017,19 +1029,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1037,19 +1049,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1057,19 +1069,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1077,19 +1089,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1097,19 +1109,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1117,19 +1129,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1137,19 +1149,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1157,19 +1169,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1177,19 +1189,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
   <si>
     <t>No.</t>
   </si>
@@ -35,39 +35,15 @@
     <t>평균</t>
   </si>
   <si>
-    <t>489.9</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.9</t>
-  </si>
-  <si>
     <t>01일</t>
   </si>
   <si>
-    <t>542.4</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
-    <t>345.6</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>8.9</t>
-  </si>
-  <si>
     <t>03일</t>
   </si>
   <si>
@@ -230,10 +206,22 @@
     <t>14일</t>
   </si>
   <si>
+    <t>579.2</t>
+  </si>
+  <si>
+    <t>6948.2</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>69.5</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>15일</t>
   </si>
   <si>
     <t>16일</t>
@@ -571,17 +559,13 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" t="s" s="25">
+      <c r="C2" s="25"/>
+      <c r="D2" t="s" s="26">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="26">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s" s="27">
-        <v>9</v>
-      </c>
+      <c r="E2" s="27"/>
       <c r="F2" t="s" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -589,59 +573,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s" s="31">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s" s="32">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s" s="34">
-        <v>12</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="36">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="37">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s" s="38">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -649,19 +617,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -669,19 +637,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -689,19 +657,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -709,19 +677,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -729,19 +697,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -749,19 +717,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -769,19 +737,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -789,19 +757,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -809,19 +777,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -829,19 +797,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -849,19 +817,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -869,19 +837,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -889,19 +857,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -909,19 +877,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -929,19 +897,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -949,19 +917,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -969,19 +937,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -989,19 +957,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1009,19 +977,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1029,19 +997,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1049,19 +1017,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1069,19 +1037,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1089,19 +1057,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1109,19 +1077,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1129,19 +1097,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1149,19 +1117,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1169,19 +1137,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1189,19 +1157,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="97">
   <si>
     <t>No.</t>
   </si>
@@ -35,15 +35,39 @@
     <t>평균</t>
   </si>
   <si>
+    <t>502.6</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>5.0</t>
+  </si>
+  <si>
     <t>01일</t>
   </si>
   <si>
+    <t>542.4</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>345.6</t>
+  </si>
+  <si>
+    <t>888.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
     <t>03일</t>
   </si>
   <si>
@@ -221,10 +245,19 @@
     <t>15일</t>
   </si>
   <si>
+    <t>590.7</t>
+  </si>
+  <si>
+    <t>7538.9</t>
+  </si>
+  <si>
+    <t>75.4</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>16일</t>
   </si>
   <si>
     <t>17일</t>
@@ -559,13 +592,17 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" t="s" s="25">
+        <v>7</v>
+      </c>
       <c r="D2" t="s" s="26">
-        <v>7</v>
-      </c>
-      <c r="E2" s="27"/>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="27">
+        <v>9</v>
+      </c>
       <c r="F2" t="s" s="28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -573,43 +610,59 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>8</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s" s="31">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s" s="32">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s" s="33">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s" s="34">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>9</v>
-      </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="36">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s" s="37">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="39">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -617,19 +670,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -637,19 +690,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -657,19 +710,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -677,19 +730,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -697,19 +750,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -717,19 +770,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -737,19 +790,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s" s="37">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s" s="38">
         <v>46</v>
       </c>
-      <c r="D12" t="s" s="37">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>38</v>
-      </c>
       <c r="F12" t="s" s="39">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -757,19 +810,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -777,19 +830,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -797,19 +850,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -817,19 +870,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -837,19 +890,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -857,19 +910,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -877,19 +930,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -897,19 +950,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -917,19 +970,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -937,19 +990,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -957,19 +1010,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -977,19 +1030,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -997,19 +1050,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1017,19 +1070,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1037,19 +1090,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1057,19 +1110,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1077,19 +1130,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1097,19 +1150,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1117,19 +1170,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1137,19 +1190,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1157,19 +1210,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="100">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>502.6</t>
+    <t>508.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.0</t>
+    <t>5.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -257,10 +257,19 @@
     <t>16일</t>
   </si>
   <si>
+    <t>589.0</t>
+  </si>
+  <si>
+    <t>8127.9</t>
+  </si>
+  <si>
+    <t>81.3</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>17일</t>
   </si>
   <si>
     <t>18일</t>
@@ -916,13 +925,13 @@
         <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -930,19 +939,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -950,19 +959,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -970,19 +979,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -990,19 +999,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1010,19 +1019,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1030,19 +1039,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1050,19 +1059,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1070,19 +1079,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1090,19 +1099,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1110,19 +1119,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1130,19 +1139,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1150,19 +1159,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1170,19 +1179,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1190,19 +1199,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1210,19 +1219,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="103">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>508.0</t>
+    <t>512.1</t>
   </si>
   <si>
     <t>-</t>
@@ -257,10 +257,10 @@
     <t>16일</t>
   </si>
   <si>
-    <t>589.0</t>
-  </si>
-  <si>
-    <t>8127.9</t>
+    <t>589.7</t>
+  </si>
+  <si>
+    <t>8128.6</t>
   </si>
   <si>
     <t>81.3</t>
@@ -269,10 +269,19 @@
     <t>17일</t>
   </si>
   <si>
+    <t>577.9</t>
+  </si>
+  <si>
+    <t>8706.5</t>
+  </si>
+  <si>
+    <t>87.1</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>18일</t>
   </si>
   <si>
     <t>19일</t>
@@ -945,13 +954,13 @@
         <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -959,19 +968,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -979,19 +988,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -999,19 +1008,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1019,19 +1028,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1039,19 +1048,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1059,19 +1068,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1079,19 +1088,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1099,19 +1108,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1119,19 +1128,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1139,19 +1148,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1159,19 +1168,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1179,19 +1188,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1199,19 +1208,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1219,19 +1228,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="107">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>512.1</t>
+    <t>515.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.1</t>
+    <t>5.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -269,10 +269,10 @@
     <t>17일</t>
   </si>
   <si>
-    <t>577.9</t>
-  </si>
-  <si>
-    <t>8706.5</t>
+    <t>578.3</t>
+  </si>
+  <si>
+    <t>8706.9</t>
   </si>
   <si>
     <t>87.1</t>
@@ -281,10 +281,22 @@
     <t>18일</t>
   </si>
   <si>
+    <t>574.9</t>
+  </si>
+  <si>
+    <t>9281.8</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>92.8</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>19일</t>
   </si>
   <si>
     <t>20일</t>
@@ -974,13 +986,13 @@
         <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -988,19 +1000,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1008,19 +1020,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1028,19 +1040,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1048,19 +1060,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1068,19 +1080,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1088,19 +1100,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1108,19 +1120,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1128,19 +1140,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1148,19 +1160,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1168,19 +1180,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1188,19 +1200,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1208,19 +1220,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1228,19 +1240,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="103">
   <si>
     <t>No.</t>
   </si>
@@ -35,39 +35,15 @@
     <t>평균</t>
   </si>
   <si>
-    <t>515.7</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.2</t>
-  </si>
-  <si>
     <t>01일</t>
   </si>
   <si>
-    <t>542.4</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
-    <t>345.6</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>8.9</t>
-  </si>
-  <si>
     <t>03일</t>
   </si>
   <si>
@@ -296,10 +272,22 @@
     <t>19일</t>
   </si>
   <si>
+    <t>335.1</t>
+  </si>
+  <si>
+    <t>9616.9</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>96.2</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>20일</t>
   </si>
   <si>
     <t>21일</t>
@@ -622,17 +610,13 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" t="s" s="25">
+      <c r="C2" s="25"/>
+      <c r="D2" t="s" s="26">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="26">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s" s="27">
-        <v>9</v>
-      </c>
+      <c r="E2" s="27"/>
       <c r="F2" t="s" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -640,59 +624,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s" s="31">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s" s="32">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s" s="34">
-        <v>12</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="36">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="37">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s" s="38">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -700,19 +668,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -720,19 +688,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -740,19 +708,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -760,19 +728,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -780,19 +748,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -800,19 +768,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -820,19 +788,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -840,19 +808,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -860,19 +828,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -880,19 +848,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -900,19 +868,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -920,19 +888,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -940,19 +908,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -960,19 +928,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -980,19 +948,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1000,19 +968,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1020,19 +988,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1040,19 +1008,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1060,19 +1028,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1080,19 +1048,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1100,19 +1068,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1120,19 +1088,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1140,19 +1108,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1160,19 +1128,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1180,19 +1148,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1200,19 +1168,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1220,19 +1188,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1240,19 +1208,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="111">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,37 @@
     <t>평균</t>
   </si>
   <si>
+    <t>506.2</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>5.1</t>
+  </si>
+  <si>
     <t>01일</t>
   </si>
   <si>
+    <t>542.4</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
     <t>02일</t>
+  </si>
+  <si>
+    <t>345.6</t>
+  </si>
+  <si>
+    <t>888.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>8.9</t>
   </si>
   <si>
     <t>03일</t>
@@ -610,13 +634,17 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" t="s" s="25">
+        <v>7</v>
+      </c>
       <c r="D2" t="s" s="26">
-        <v>7</v>
-      </c>
-      <c r="E2" s="27"/>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="27">
+        <v>9</v>
+      </c>
       <c r="F2" t="s" s="28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -624,43 +652,59 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>8</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s" s="31">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s" s="32">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s" s="33">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s" s="34">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>9</v>
-      </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="36">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s" s="37">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="39">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -668,19 +712,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -688,19 +732,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -708,19 +752,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -728,19 +772,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -748,19 +792,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -768,19 +812,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -788,19 +832,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s" s="37">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s" s="38">
         <v>46</v>
       </c>
-      <c r="D12" t="s" s="37">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>38</v>
-      </c>
       <c r="F12" t="s" s="39">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -808,19 +852,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -828,19 +872,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -848,19 +892,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -868,19 +912,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -888,19 +932,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -908,19 +952,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -928,19 +972,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -948,19 +992,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -968,19 +1012,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -988,19 +1032,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1008,19 +1052,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1028,19 +1072,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1048,19 +1092,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1068,19 +1112,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1088,19 +1132,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1108,19 +1152,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1128,19 +1172,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1148,19 +1192,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1168,19 +1212,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1188,19 +1232,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1208,19 +1252,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>506.2</t>
+    <t>484.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.1</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -209,9 +209,6 @@
     <t>5779.1</t>
   </si>
   <si>
-    <t>4.8</t>
-  </si>
-  <si>
     <t>57.8</t>
   </si>
   <si>
@@ -311,10 +308,22 @@
     <t>20일</t>
   </si>
   <si>
+    <t>64.3</t>
+  </si>
+  <si>
+    <t>9681.2</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>96.8</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>21일</t>
   </si>
   <si>
     <t>22일</t>
@@ -881,10 +890,10 @@
         <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s" s="39">
         <v>65</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -892,19 +901,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>67</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>68</v>
-      </c>
-      <c r="D15" t="s" s="32">
-        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
         <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -912,19 +921,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>71</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>72</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>73</v>
       </c>
-      <c r="E16" t="s" s="38">
+      <c r="F16" t="s" s="39">
         <v>74</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -932,19 +941,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>76</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>77</v>
-      </c>
-      <c r="D17" t="s" s="32">
-        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
         <v>46</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -952,19 +961,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>80</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>81</v>
-      </c>
-      <c r="D18" t="s" s="37">
-        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
         <v>46</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -972,19 +981,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>84</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>85</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
+        <v>73</v>
+      </c>
+      <c r="F19" t="s" s="34">
         <v>86</v>
-      </c>
-      <c r="E19" t="s" s="33">
-        <v>74</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -992,19 +1001,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>88</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>89</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
         <v>90</v>
       </c>
-      <c r="E20" t="s" s="38">
+      <c r="F20" t="s" s="39">
         <v>91</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1012,19 +1021,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>93</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>94</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>95</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>96</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1032,19 +1041,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>98</v>
-      </c>
-      <c r="C22" t="s" s="36">
-        <v>99</v>
       </c>
       <c r="D22" t="s" s="37">
         <v>99</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1052,19 +1061,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1072,19 +1081,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1092,19 +1101,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1112,19 +1121,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1132,19 +1141,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1152,19 +1161,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1172,19 +1181,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1192,19 +1201,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1212,19 +1221,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1232,19 +1241,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1252,19 +1261,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="119">
   <si>
     <t>No.</t>
   </si>
@@ -35,180 +35,183 @@
     <t>평균</t>
   </si>
   <si>
-    <t>484.1</t>
+    <t>467.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>542.4</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>345.6</t>
+  </si>
+  <si>
+    <t>888.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>100.9</t>
+  </si>
+  <si>
+    <t>988.9</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>9.9</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>627.2</t>
+  </si>
+  <si>
+    <t>1616.1</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>16.2</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>639.8</t>
+  </si>
+  <si>
+    <t>2255.9</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>597.3</t>
+  </si>
+  <si>
+    <t>2853.2</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>389.1</t>
+  </si>
+  <si>
+    <t>3242.3</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>32.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>591.1</t>
+  </si>
+  <si>
+    <t>3833.4</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>38.3</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>619.3</t>
+  </si>
+  <si>
+    <t>4452.7</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>585.4</t>
+  </si>
+  <si>
+    <t>5038.1</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>256.0</t>
+  </si>
+  <si>
+    <t>5294.1</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>52.9</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>485.0</t>
+  </si>
+  <si>
+    <t>5779.1</t>
+  </si>
+  <si>
     <t>4.8</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>542.4</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>345.6</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>8.9</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>100.9</t>
-  </si>
-  <si>
-    <t>988.9</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>9.9</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>627.2</t>
-  </si>
-  <si>
-    <t>1616.1</t>
-  </si>
-  <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>16.2</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>639.8</t>
-  </si>
-  <si>
-    <t>2255.9</t>
-  </si>
-  <si>
-    <t>6.4</t>
-  </si>
-  <si>
-    <t>22.6</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>597.3</t>
-  </si>
-  <si>
-    <t>2853.2</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>28.5</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>389.1</t>
-  </si>
-  <si>
-    <t>3242.3</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>32.4</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>591.1</t>
-  </si>
-  <si>
-    <t>3833.4</t>
-  </si>
-  <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>38.3</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>619.3</t>
-  </si>
-  <si>
-    <t>4452.7</t>
-  </si>
-  <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>44.5</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>585.4</t>
-  </si>
-  <si>
-    <t>5038.1</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>256.0</t>
-  </si>
-  <si>
-    <t>5294.1</t>
-  </si>
-  <si>
-    <t>2.6</t>
-  </si>
-  <si>
-    <t>52.9</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>485.0</t>
-  </si>
-  <si>
-    <t>5779.1</t>
-  </si>
-  <si>
     <t>57.8</t>
   </si>
   <si>
@@ -323,10 +326,22 @@
     <t>21일</t>
   </si>
   <si>
+    <t>137.5</t>
+  </si>
+  <si>
+    <t>9818.7</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>98.2</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>22일</t>
   </si>
   <si>
     <t>23일</t>
@@ -890,10 +905,10 @@
         <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -901,19 +916,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
         <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -921,19 +936,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -941,19 +956,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
         <v>46</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -961,19 +976,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
         <v>46</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -981,19 +996,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1001,19 +1016,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1021,19 +1036,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1041,19 +1056,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1061,19 +1076,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1081,19 +1096,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1101,19 +1116,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1121,19 +1136,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1141,19 +1156,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1161,19 +1176,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1181,19 +1196,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1201,19 +1216,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1221,19 +1236,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1241,19 +1256,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1261,19 +1276,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="122">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>467.6</t>
+    <t>473.7</t>
   </si>
   <si>
     <t>-</t>
@@ -341,10 +341,19 @@
     <t>22일</t>
   </si>
   <si>
+    <t>603.8</t>
+  </si>
+  <si>
+    <t>10422.5</t>
+  </si>
+  <si>
+    <t>104.2</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>23일</t>
   </si>
   <si>
     <t>24일</t>
@@ -1102,13 +1111,13 @@
         <v>109</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1116,19 +1125,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1136,19 +1145,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1156,19 +1165,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1176,19 +1185,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1196,19 +1205,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1216,19 +1225,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1236,19 +1245,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1256,19 +1265,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1276,19 +1285,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="126">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>473.7</t>
+    <t>473.1</t>
   </si>
   <si>
     <t>-</t>
@@ -353,10 +353,22 @@
     <t>23일</t>
   </si>
   <si>
+    <t>459.8</t>
+  </si>
+  <si>
+    <t>10882.3</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>108.8</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>24일</t>
   </si>
   <si>
     <t>25일</t>
@@ -1131,13 +1143,13 @@
         <v>113</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1145,19 +1157,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1165,19 +1177,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1185,19 +1197,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1205,19 +1217,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1225,19 +1237,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1245,19 +1257,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1265,19 +1277,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1285,19 +1297,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>473.1</t>
+    <t>478.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -209,9 +209,6 @@
     <t>5779.1</t>
   </si>
   <si>
-    <t>4.8</t>
-  </si>
-  <si>
     <t>57.8</t>
   </si>
   <si>
@@ -353,10 +350,10 @@
     <t>23일</t>
   </si>
   <si>
-    <t>459.8</t>
-  </si>
-  <si>
-    <t>10882.3</t>
+    <t>460.1</t>
+  </si>
+  <si>
+    <t>10882.6</t>
   </si>
   <si>
     <t>4.6</t>
@@ -368,10 +365,19 @@
     <t>24일</t>
   </si>
   <si>
+    <t>599.3</t>
+  </si>
+  <si>
+    <t>11481.9</t>
+  </si>
+  <si>
+    <t>114.8</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>25일</t>
   </si>
   <si>
     <t>26일</t>
@@ -926,10 +932,10 @@
         <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s" s="39">
         <v>65</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -937,19 +943,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>67</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>68</v>
-      </c>
-      <c r="D15" t="s" s="32">
-        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
         <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -957,19 +963,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>71</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>72</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>73</v>
       </c>
-      <c r="E16" t="s" s="38">
+      <c r="F16" t="s" s="39">
         <v>74</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -977,19 +983,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>76</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>77</v>
-      </c>
-      <c r="D17" t="s" s="32">
-        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
         <v>46</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -997,19 +1003,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>80</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>81</v>
-      </c>
-      <c r="D18" t="s" s="37">
-        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
         <v>46</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1017,19 +1023,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>84</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>85</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
+        <v>73</v>
+      </c>
+      <c r="F19" t="s" s="34">
         <v>86</v>
-      </c>
-      <c r="E19" t="s" s="33">
-        <v>74</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1037,19 +1043,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>88</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>89</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
         <v>90</v>
       </c>
-      <c r="E20" t="s" s="38">
+      <c r="F20" t="s" s="39">
         <v>91</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1057,19 +1063,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>93</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>94</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
         <v>95</v>
       </c>
-      <c r="E21" t="s" s="33">
+      <c r="F21" t="s" s="34">
         <v>96</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1077,19 +1083,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>98</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>99</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>100</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>101</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1097,19 +1103,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>102</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>103</v>
       </c>
-      <c r="C23" t="s" s="31">
+      <c r="D23" t="s" s="32">
         <v>104</v>
       </c>
-      <c r="D23" t="s" s="32">
+      <c r="E23" t="s" s="33">
         <v>105</v>
       </c>
-      <c r="E23" t="s" s="33">
+      <c r="F23" t="s" s="34">
         <v>106</v>
-      </c>
-      <c r="F23" t="s" s="34">
-        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1117,19 +1123,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s" s="36">
         <v>108</v>
       </c>
-      <c r="C24" t="s" s="36">
+      <c r="D24" t="s" s="37">
         <v>109</v>
-      </c>
-      <c r="D24" t="s" s="37">
-        <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
         <v>36</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1137,19 +1143,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
+        <v>111</v>
+      </c>
+      <c r="C25" t="s" s="31">
         <v>112</v>
       </c>
-      <c r="C25" t="s" s="31">
+      <c r="D25" t="s" s="32">
         <v>113</v>
       </c>
-      <c r="D25" t="s" s="32">
+      <c r="E25" t="s" s="33">
         <v>114</v>
       </c>
-      <c r="E25" t="s" s="33">
+      <c r="F25" t="s" s="34">
         <v>115</v>
-      </c>
-      <c r="F25" t="s" s="34">
-        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1157,19 +1163,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
+        <v>116</v>
+      </c>
+      <c r="C26" t="s" s="36">
         <v>117</v>
-      </c>
-      <c r="C26" t="s" s="36">
-        <v>118</v>
       </c>
       <c r="D26" t="s" s="37">
         <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1177,19 +1183,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1197,19 +1203,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1217,19 +1223,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1237,19 +1243,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1257,19 +1263,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1277,19 +1283,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1297,19 +1303,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>478.4</t>
+    <t>480.5</t>
   </si>
   <si>
     <t>-</t>
@@ -377,10 +377,22 @@
     <t>25일</t>
   </si>
   <si>
+    <t>531.5</t>
+  </si>
+  <si>
+    <t>12013.4</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>120.1</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>26일</t>
   </si>
   <si>
     <t>27일</t>
@@ -1189,13 +1201,13 @@
         <v>121</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1203,19 +1215,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1223,19 +1235,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1243,19 +1255,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1263,19 +1275,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1283,19 +1295,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1303,19 +1315,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="125">
   <si>
     <t>No.</t>
   </si>
@@ -35,178 +35,157 @@
     <t>평균</t>
   </si>
   <si>
-    <t>480.5</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>100.9</t>
+  </si>
+  <si>
+    <t>988.9</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>9.9</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>627.2</t>
+  </si>
+  <si>
+    <t>1616.1</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>16.2</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>639.8</t>
+  </si>
+  <si>
+    <t>2255.9</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>597.3</t>
+  </si>
+  <si>
+    <t>2853.2</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>389.1</t>
+  </si>
+  <si>
+    <t>3242.3</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>32.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>591.1</t>
+  </si>
+  <si>
+    <t>3833.4</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>38.3</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>619.3</t>
+  </si>
+  <si>
+    <t>4452.7</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>585.4</t>
+  </si>
+  <si>
+    <t>5038.1</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>256.0</t>
+  </si>
+  <si>
+    <t>5294.1</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>52.9</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>485.0</t>
+  </si>
+  <si>
+    <t>5779.1</t>
+  </si>
+  <si>
     <t>4.8</t>
-  </si>
-  <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>542.4</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>345.6</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>8.9</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>100.9</t>
-  </si>
-  <si>
-    <t>988.9</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>9.9</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>627.2</t>
-  </si>
-  <si>
-    <t>1616.1</t>
-  </si>
-  <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>16.2</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>639.8</t>
-  </si>
-  <si>
-    <t>2255.9</t>
-  </si>
-  <si>
-    <t>6.4</t>
-  </si>
-  <si>
-    <t>22.6</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>597.3</t>
-  </si>
-  <si>
-    <t>2853.2</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>28.5</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>389.1</t>
-  </si>
-  <si>
-    <t>3242.3</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>32.4</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>591.1</t>
-  </si>
-  <si>
-    <t>3833.4</t>
-  </si>
-  <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>38.3</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>619.3</t>
-  </si>
-  <si>
-    <t>4452.7</t>
-  </si>
-  <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>44.5</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>585.4</t>
-  </si>
-  <si>
-    <t>5038.1</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>256.0</t>
-  </si>
-  <si>
-    <t>5294.1</t>
-  </si>
-  <si>
-    <t>2.6</t>
-  </si>
-  <si>
-    <t>52.9</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>485.0</t>
-  </si>
-  <si>
-    <t>5779.1</t>
   </si>
   <si>
     <t>57.8</t>
@@ -697,17 +676,13 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" t="s" s="25">
+      <c r="C2" s="25"/>
+      <c r="D2" t="s" s="26">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="26">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s" s="27">
-        <v>9</v>
-      </c>
+      <c r="E2" s="27"/>
       <c r="F2" t="s" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -715,59 +690,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s" s="31">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s" s="32">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s" s="34">
-        <v>12</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="36">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="37">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s" s="38">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -775,19 +734,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -795,19 +754,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -815,19 +774,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -835,19 +794,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -855,19 +814,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -875,19 +834,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -895,19 +854,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -915,19 +874,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -935,19 +894,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -955,19 +914,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -975,19 +934,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -995,19 +954,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1015,19 +974,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1035,19 +994,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1055,19 +1014,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1075,19 +1034,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1095,19 +1054,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1115,19 +1074,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1135,19 +1094,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1155,19 +1114,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1175,19 +1134,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1195,19 +1154,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1215,19 +1174,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1235,19 +1194,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1255,19 +1214,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1275,19 +1234,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1295,19 +1254,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1315,19 +1274,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="141">
   <si>
     <t>No.</t>
   </si>
@@ -35,15 +35,39 @@
     <t>평균</t>
   </si>
   <si>
+    <t>468.0</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.7</t>
+  </si>
+  <si>
     <t>01일</t>
   </si>
   <si>
+    <t>542.4</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>345.6</t>
+  </si>
+  <si>
+    <t>888.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
     <t>03일</t>
   </si>
   <si>
@@ -371,13 +395,37 @@
     <t>26일</t>
   </si>
   <si>
+    <t>445.7</t>
+  </si>
+  <si>
+    <t>12459.1</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>124.6</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
+    <t>176.3</t>
+  </si>
+  <si>
+    <t>12635.4</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>126.4</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>27일</t>
-  </si>
-  <si>
-    <t>28일</t>
   </si>
   <si>
     <t>29일</t>
@@ -676,13 +724,17 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" t="s" s="25">
+        <v>7</v>
+      </c>
       <c r="D2" t="s" s="26">
-        <v>7</v>
-      </c>
-      <c r="E2" s="27"/>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="27">
+        <v>9</v>
+      </c>
       <c r="F2" t="s" s="28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -690,43 +742,59 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>8</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s" s="31">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s" s="32">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s" s="33">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s" s="34">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>9</v>
-      </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="36">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s" s="37">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="39">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -734,19 +802,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -754,19 +822,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -774,19 +842,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -794,19 +862,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -814,19 +882,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -834,19 +902,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -854,19 +922,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s" s="37">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s" s="38">
         <v>46</v>
       </c>
-      <c r="D12" t="s" s="37">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>38</v>
-      </c>
       <c r="F12" t="s" s="39">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -874,19 +942,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -894,19 +962,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -914,19 +982,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -934,19 +1002,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -954,19 +1022,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -974,19 +1042,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -994,19 +1062,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1014,19 +1082,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1034,19 +1102,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1054,19 +1122,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1074,19 +1142,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1094,19 +1162,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1114,19 +1182,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1134,19 +1202,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1154,19 +1222,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1174,19 +1242,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1194,19 +1262,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>119</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1214,19 +1282,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>119</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1234,19 +1302,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>119</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1254,19 +1322,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>119</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1274,19 +1342,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>119</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="137">
   <si>
     <t>No.</t>
   </si>
@@ -35,39 +35,15 @@
     <t>평균</t>
   </si>
   <si>
-    <t>468.0</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
-  </si>
-  <si>
     <t>01일</t>
   </si>
   <si>
-    <t>542.4</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
-    <t>345.6</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>8.9</t>
-  </si>
-  <si>
     <t>03일</t>
   </si>
   <si>
@@ -425,10 +401,22 @@
     <t>28일</t>
   </si>
   <si>
+    <t>305.9</t>
+  </si>
+  <si>
+    <t>12941.3</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>129.4</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>29일</t>
   </si>
   <si>
     <t>30일</t>
@@ -724,17 +712,13 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" t="s" s="25">
+      <c r="C2" s="25"/>
+      <c r="D2" t="s" s="26">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="26">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s" s="27">
-        <v>9</v>
-      </c>
+      <c r="E2" s="27"/>
       <c r="F2" t="s" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -742,59 +726,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s" s="31">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s" s="32">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s" s="34">
-        <v>12</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="36">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="37">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s" s="38">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -802,19 +770,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -822,19 +790,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -842,19 +810,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -862,19 +830,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -882,19 +850,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -902,19 +870,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -922,19 +890,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -942,19 +910,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -962,19 +930,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -982,19 +950,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -1002,19 +970,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1022,19 +990,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1042,19 +1010,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1062,19 +1030,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1082,19 +1050,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1102,19 +1070,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1122,19 +1090,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1142,19 +1110,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1162,19 +1130,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1182,19 +1150,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1202,19 +1170,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1222,19 +1190,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1242,19 +1210,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1262,19 +1230,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1282,19 +1250,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1302,19 +1270,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1322,19 +1290,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1342,19 +1310,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="148">
   <si>
     <t>No.</t>
   </si>
@@ -35,15 +35,39 @@
     <t>평균</t>
   </si>
   <si>
+    <t>466.1</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.7</t>
+  </si>
+  <si>
     <t>01일</t>
   </si>
   <si>
+    <t>542.4</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>345.6</t>
+  </si>
+  <si>
+    <t>888.0</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
     <t>03일</t>
   </si>
   <si>
@@ -416,10 +440,19 @@
     <t>29일</t>
   </si>
   <si>
+    <t>575.1</t>
+  </si>
+  <si>
+    <t>13516.4</t>
+  </si>
+  <si>
+    <t>135.2</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>30일</t>
   </si>
   <si>
     <t>31일</t>
@@ -712,13 +745,17 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" t="s" s="25">
+        <v>7</v>
+      </c>
       <c r="D2" t="s" s="26">
-        <v>7</v>
-      </c>
-      <c r="E2" s="27"/>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="27">
+        <v>9</v>
+      </c>
       <c r="F2" t="s" s="28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -726,43 +763,59 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>8</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s" s="31">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s" s="32">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s" s="33">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s" s="34">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>9</v>
-      </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="36">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s" s="37">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="38">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="39">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -770,19 +823,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -790,19 +843,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -810,19 +863,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -830,19 +883,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -850,19 +903,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -870,19 +923,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -890,19 +943,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="36">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s" s="37">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s" s="38">
         <v>46</v>
       </c>
-      <c r="D12" t="s" s="37">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s" s="38">
-        <v>38</v>
-      </c>
       <c r="F12" t="s" s="39">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -910,19 +963,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -930,19 +983,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -950,19 +1003,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -970,19 +1023,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -990,19 +1043,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1010,19 +1063,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1030,19 +1083,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1050,19 +1103,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1070,19 +1123,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1090,19 +1143,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1110,19 +1163,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1130,19 +1183,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1150,19 +1203,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1170,19 +1223,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1190,19 +1243,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1210,19 +1263,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1230,19 +1283,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1250,19 +1303,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1270,19 +1323,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1290,19 +1343,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1310,19 +1363,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>466.1</t>
+    <t>470.3</t>
   </si>
   <si>
     <t>-</t>
@@ -452,10 +452,19 @@
     <t>30일</t>
   </si>
   <si>
+    <t>593.6</t>
+  </si>
+  <si>
+    <t>14110.0</t>
+  </si>
+  <si>
+    <t>141.1</t>
+  </si>
+  <si>
+    <t>31일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>31일</t>
   </si>
 </sst>
 </file>
@@ -1349,13 +1358,13 @@
         <v>146</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1363,19 +1372,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8023/2026-05-01.xlsx
+++ b/past_data/site_8023/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="145">
   <si>
     <t>No.</t>
   </si>
@@ -35,39 +35,15 @@
     <t>평균</t>
   </si>
   <si>
-    <t>470.3</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
-  </si>
-  <si>
     <t>01일</t>
   </si>
   <si>
-    <t>542.4</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
-    <t>345.6</t>
-  </si>
-  <si>
-    <t>888.0</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>8.9</t>
-  </si>
-  <si>
     <t>03일</t>
   </si>
   <si>
@@ -452,10 +428,10 @@
     <t>30일</t>
   </si>
   <si>
-    <t>593.6</t>
-  </si>
-  <si>
-    <t>14110.0</t>
+    <t>593.8</t>
+  </si>
+  <si>
+    <t>14110.2</t>
   </si>
   <si>
     <t>141.1</t>
@@ -464,7 +440,13 @@
     <t>31일</t>
   </si>
   <si>
-    <t>0.0</t>
+    <t>591.6</t>
+  </si>
+  <si>
+    <t>14701.8</t>
+  </si>
+  <si>
+    <t>147.0</t>
   </si>
 </sst>
 </file>
@@ -754,17 +736,13 @@
       <c r="B2" t="s" s="24">
         <v>6</v>
       </c>
-      <c r="C2" t="s" s="25">
+      <c r="C2" s="25"/>
+      <c r="D2" t="s" s="26">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="26">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s" s="27">
-        <v>9</v>
-      </c>
+      <c r="E2" s="27"/>
       <c r="F2" t="s" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1">
@@ -772,59 +750,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="30">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s" s="31">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s" s="32">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s" s="33">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s" s="34">
-        <v>12</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" t="n" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="36">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="37">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s" s="38">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" t="n" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -832,19 +794,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -852,19 +814,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -872,19 +834,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -892,19 +854,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -912,19 +874,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -932,19 +894,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -952,19 +914,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -972,19 +934,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -992,19 +954,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -1012,19 +974,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -1032,19 +994,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1052,19 +1014,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1072,19 +1034,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1092,19 +1054,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1112,19 +1074,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1132,19 +1094,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1152,19 +1114,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1172,19 +1134,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1192,19 +1154,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1212,19 +1174,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1232,19 +1194,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1252,19 +1214,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1272,19 +1234,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1292,19 +1254,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1312,19 +1274,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1332,19 +1294,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1352,19 +1314,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1372,19 +1334,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
